--- a/docs/Lab02/Lab02_BBT_TCs_Form.xlsx
+++ b/docs/Lab02/Lab02_BBT_TCs_Form.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\margi\OneDrive\Desktop\FACULTATE\AN 3 - SEMESTRUL 2\VVSS - Lab\MyDrinkShop\docs\Lab02\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Alex\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF1B0059-EA8E-4A65-BE1E-16813E498C46}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{611E4D6C-9673-423B-8E42-1DE3155606B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Statement" sheetId="1" r:id="rId1"/>
@@ -90,7 +90,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="238" uniqueCount="105">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="241" uniqueCount="108">
   <si>
     <t>VVSS, Info Romana, 2025-2026</t>
   </si>
@@ -405,6 +405,15 @@
   </si>
   <si>
     <t>04. price = 0.01</t>
+  </si>
+  <si>
+    <t>Mărcuș Alexandru Marian</t>
+  </si>
+  <si>
+    <t>Mărginean Dan</t>
+  </si>
+  <si>
+    <t>Marinescu Dragoș</t>
   </si>
 </sst>
 </file>
@@ -1104,19 +1113,122 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="17" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1128,123 +1240,20 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1553,36 +1562,36 @@
     <tabColor rgb="FF0070C0"/>
   </sheetPr>
   <dimension ref="A1:O26"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="4" max="4" width="22.5703125" customWidth="1"/>
-    <col min="9" max="9" width="32.85546875" customWidth="1"/>
-    <col min="10" max="10" width="10.5703125" customWidth="1"/>
-    <col min="12" max="12" width="12.140625" customWidth="1"/>
+    <col min="4" max="4" width="22.5546875" customWidth="1"/>
+    <col min="9" max="9" width="32.88671875" customWidth="1"/>
+    <col min="10" max="10" width="10.5546875" customWidth="1"/>
+    <col min="12" max="12" width="12.109375" customWidth="1"/>
     <col min="14" max="14" width="20" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="C1" s="89" t="s">
+    <row r="1" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="C1" s="64" t="s">
         <v>0</v>
       </c>
-      <c r="D1" s="77"/>
-      <c r="E1" s="77"/>
-      <c r="F1" s="58"/>
+      <c r="D1" s="58"/>
+      <c r="E1" s="58"/>
+      <c r="F1" s="59"/>
       <c r="H1" s="51" t="s">
         <v>51</v>
       </c>
       <c r="I1" s="51"/>
       <c r="J1" s="51"/>
     </row>
-    <row r="2" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="H2" s="93" t="s">
+    <row r="2" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="H2" s="62" t="s">
         <v>52</v>
       </c>
-      <c r="I2" s="77"/>
-      <c r="J2" s="58"/>
-    </row>
-    <row r="3" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="I2" s="58"/>
+      <c r="J2" s="59"/>
+    </row>
+    <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="H3" s="2"/>
       <c r="I3" s="2" t="s">
         <v>53</v>
@@ -1591,62 +1600,74 @@
         <v>54</v>
       </c>
     </row>
-    <row r="4" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:10" x14ac:dyDescent="0.3">
       <c r="H4" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="I4" s="2"/>
-      <c r="J4" s="2"/>
-    </row>
-    <row r="5" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="I4" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="J4" s="2">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="5" spans="2:10" x14ac:dyDescent="0.3">
       <c r="H5" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="I5" s="2"/>
-      <c r="J5" s="2"/>
-    </row>
-    <row r="6" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="I5" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="J5" s="2">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="6" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B6" s="37"/>
       <c r="H6" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="I6" s="2"/>
-      <c r="J6" s="2"/>
-    </row>
-    <row r="7" spans="2:10" ht="14.45" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="8" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="I6" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="J6" s="2">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="7" spans="2:10" ht="14.4" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="8" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B8" s="49" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="9" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B9" s="1" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="10" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B10" s="1" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="11" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B11" s="1" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="12" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B12" s="1"/>
       <c r="C12" s="1"/>
       <c r="D12" s="1"/>
       <c r="E12" s="1"/>
     </row>
-    <row r="13" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B13" s="1"/>
       <c r="C13" s="1"/>
       <c r="D13" s="1"/>
       <c r="E13" s="1"/>
     </row>
-    <row r="14" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B14" t="s">
         <v>62</v>
       </c>
@@ -1654,7 +1675,7 @@
       <c r="D14" s="1"/>
       <c r="E14" s="1"/>
     </row>
-    <row r="15" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B15" t="s">
         <v>63</v>
       </c>
@@ -1662,7 +1683,7 @@
       <c r="D15" s="1"/>
       <c r="E15" s="1"/>
     </row>
-    <row r="16" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B16" t="s">
         <v>64</v>
       </c>
@@ -1670,32 +1691,32 @@
       <c r="D16" s="1"/>
       <c r="E16" s="1"/>
     </row>
-    <row r="17" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:15" x14ac:dyDescent="0.3">
       <c r="B17" s="1"/>
       <c r="D17" s="1"/>
       <c r="E17" s="1"/>
     </row>
-    <row r="18" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:15" x14ac:dyDescent="0.3">
       <c r="B18" s="49" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="19" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:15" x14ac:dyDescent="0.3">
       <c r="B19" s="1" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="20" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:15" x14ac:dyDescent="0.3">
       <c r="C20" s="47" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="21" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:15" x14ac:dyDescent="0.3">
       <c r="B21" s="1" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="22" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:15" x14ac:dyDescent="0.3">
       <c r="B22" s="1" t="s">
         <v>69</v>
       </c>
@@ -1712,7 +1733,7 @@
       <c r="N22" s="1"/>
       <c r="O22" s="1"/>
     </row>
-    <row r="23" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:15" x14ac:dyDescent="0.3">
       <c r="B23" s="1" t="s">
         <v>70</v>
       </c>
@@ -1729,25 +1750,25 @@
       <c r="N23" s="1"/>
       <c r="O23" s="1"/>
     </row>
-    <row r="24" spans="1:15" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:15" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="48"/>
-      <c r="B24" s="92" t="s">
+      <c r="B24" s="74" t="s">
         <v>71</v>
       </c>
-      <c r="C24" s="66"/>
-      <c r="D24" s="66"/>
-      <c r="E24" s="66"/>
-      <c r="F24" s="66"/>
-      <c r="G24" s="66"/>
-      <c r="H24" s="66"/>
-      <c r="I24" s="66"/>
-      <c r="J24" s="66"/>
-      <c r="K24" s="66"/>
-      <c r="L24" s="66"/>
-      <c r="M24" s="66"/>
-      <c r="N24" s="66"/>
-    </row>
-    <row r="26" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="C24" s="67"/>
+      <c r="D24" s="67"/>
+      <c r="E24" s="67"/>
+      <c r="F24" s="67"/>
+      <c r="G24" s="67"/>
+      <c r="H24" s="67"/>
+      <c r="I24" s="67"/>
+      <c r="J24" s="67"/>
+      <c r="K24" s="67"/>
+      <c r="L24" s="67"/>
+      <c r="M24" s="67"/>
+      <c r="N24" s="67"/>
+    </row>
+    <row r="26" spans="1:15" x14ac:dyDescent="0.3">
       <c r="C26" s="50"/>
     </row>
   </sheetData>
@@ -1757,7 +1778,7 @@
     <mergeCell ref="H2:J2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -1767,63 +1788,63 @@
     <tabColor theme="9" tint="0.59999389629810485"/>
   </sheetPr>
   <dimension ref="B1:Q22"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="10.140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="18.140625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="19.85546875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="5.85546875" customWidth="1"/>
+    <col min="2" max="2" width="10.109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="18.109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="19.88671875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="5.88671875" customWidth="1"/>
     <col min="7" max="7" width="8" customWidth="1"/>
-    <col min="8" max="8" width="11.85546875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="11.5703125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="25.5703125" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="9.85546875" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="12.85546875" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="8.85546875" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="29.42578125" customWidth="1"/>
+    <col min="8" max="8" width="11.88671875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="11.5546875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="25.5546875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="9.88671875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="12.88671875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="8.88671875" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="29.44140625" customWidth="1"/>
     <col min="17" max="17" width="5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B1" s="89" t="s">
+    <row r="1" spans="2:17" x14ac:dyDescent="0.3">
+      <c r="B1" s="64" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="77"/>
-      <c r="D1" s="77"/>
-      <c r="E1" s="58"/>
-    </row>
-    <row r="3" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B3" s="102" t="s">
+      <c r="C1" s="58"/>
+      <c r="D1" s="58"/>
+      <c r="E1" s="59"/>
+    </row>
+    <row r="3" spans="2:17" x14ac:dyDescent="0.3">
+      <c r="B3" s="57" t="s">
         <v>72</v>
       </c>
-      <c r="C3" s="77"/>
-      <c r="D3" s="77"/>
-      <c r="E3" s="77"/>
-      <c r="F3" s="77"/>
-      <c r="G3" s="58"/>
-    </row>
-    <row r="5" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B5" s="95" t="s">
+      <c r="C3" s="58"/>
+      <c r="D3" s="58"/>
+      <c r="E3" s="58"/>
+      <c r="F3" s="58"/>
+      <c r="G3" s="59"/>
+    </row>
+    <row r="5" spans="2:17" x14ac:dyDescent="0.3">
+      <c r="B5" s="72" t="s">
         <v>73</v>
       </c>
-      <c r="C5" s="77"/>
-      <c r="D5" s="77"/>
-      <c r="E5" s="58"/>
-      <c r="G5" s="100" t="s">
+      <c r="C5" s="58"/>
+      <c r="D5" s="58"/>
+      <c r="E5" s="59"/>
+      <c r="G5" s="68" t="s">
         <v>74</v>
       </c>
-      <c r="H5" s="77"/>
-      <c r="I5" s="77"/>
-      <c r="J5" s="77"/>
-      <c r="K5" s="77"/>
-      <c r="L5" s="77"/>
-      <c r="M5" s="77"/>
-      <c r="N5" s="77"/>
-      <c r="O5" s="77"/>
-      <c r="P5" s="77"/>
-      <c r="Q5" s="58"/>
-    </row>
-    <row r="6" spans="2:17" x14ac:dyDescent="0.25">
+      <c r="H5" s="58"/>
+      <c r="I5" s="58"/>
+      <c r="J5" s="58"/>
+      <c r="K5" s="58"/>
+      <c r="L5" s="58"/>
+      <c r="M5" s="58"/>
+      <c r="N5" s="58"/>
+      <c r="O5" s="58"/>
+      <c r="P5" s="58"/>
+      <c r="Q5" s="59"/>
+    </row>
+    <row r="6" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B6" s="23" t="s">
         <v>75</v>
       </c>
@@ -1836,31 +1857,31 @@
       <c r="E6" s="23" t="s">
         <v>78</v>
       </c>
-      <c r="G6" s="52" t="s">
+      <c r="G6" s="73" t="s">
         <v>79</v>
       </c>
-      <c r="H6" s="76" t="s">
+      <c r="H6" s="70" t="s">
         <v>80</v>
       </c>
-      <c r="I6" s="76" t="s">
+      <c r="I6" s="70" t="s">
         <v>6</v>
       </c>
-      <c r="J6" s="77"/>
-      <c r="K6" s="77"/>
-      <c r="L6" s="77"/>
-      <c r="M6" s="77"/>
-      <c r="N6" s="77"/>
-      <c r="O6" s="58"/>
-      <c r="P6" s="76" t="s">
+      <c r="J6" s="58"/>
+      <c r="K6" s="58"/>
+      <c r="L6" s="58"/>
+      <c r="M6" s="58"/>
+      <c r="N6" s="58"/>
+      <c r="O6" s="59"/>
+      <c r="P6" s="70" t="s">
         <v>7</v>
       </c>
-      <c r="Q6" s="58"/>
-    </row>
-    <row r="7" spans="2:17" x14ac:dyDescent="0.25">
+      <c r="Q6" s="59"/>
+    </row>
+    <row r="7" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B7" s="4" t="s">
         <v>75</v>
       </c>
-      <c r="C7" s="96" t="s">
+      <c r="C7" s="60" t="s">
         <v>76</v>
       </c>
       <c r="D7" s="4" t="s">
@@ -1869,8 +1890,8 @@
       <c r="E7" s="4" t="s">
         <v>78</v>
       </c>
-      <c r="G7" s="53"/>
-      <c r="H7" s="53"/>
+      <c r="G7" s="61"/>
+      <c r="H7" s="61"/>
       <c r="I7" s="23" t="s">
         <v>8</v>
       </c>
@@ -1886,20 +1907,20 @@
       <c r="M7" s="23" t="s">
         <v>12</v>
       </c>
-      <c r="N7" s="76" t="s">
+      <c r="N7" s="70" t="s">
         <v>13</v>
       </c>
-      <c r="O7" s="58"/>
-      <c r="P7" s="76" t="s">
+      <c r="O7" s="59"/>
+      <c r="P7" s="70" t="s">
         <v>14</v>
       </c>
-      <c r="Q7" s="58"/>
-    </row>
-    <row r="8" spans="2:17" x14ac:dyDescent="0.25">
+      <c r="Q7" s="59"/>
+    </row>
+    <row r="8" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B8" s="4">
         <v>1</v>
       </c>
-      <c r="C8" s="53"/>
+      <c r="C8" s="61"/>
       <c r="D8" s="4" t="s">
         <v>81</v>
       </c>
@@ -1927,20 +1948,20 @@
       <c r="M8" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="N8" s="93" t="s">
+      <c r="N8" s="62" t="s">
         <v>84</v>
       </c>
-      <c r="O8" s="58"/>
-      <c r="P8" s="93" t="s">
+      <c r="O8" s="59"/>
+      <c r="P8" s="62" t="s">
         <v>23</v>
       </c>
-      <c r="Q8" s="58"/>
-    </row>
-    <row r="9" spans="2:17" x14ac:dyDescent="0.25">
+      <c r="Q8" s="59"/>
+    </row>
+    <row r="9" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B9" s="4">
         <v>2</v>
       </c>
-      <c r="C9" s="96" t="s">
+      <c r="C9" s="60" t="s">
         <v>85</v>
       </c>
       <c r="D9" s="4" t="s">
@@ -1968,20 +1989,20 @@
       <c r="M9" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="N9" s="93" t="s">
+      <c r="N9" s="62" t="s">
         <v>84</v>
       </c>
-      <c r="O9" s="58"/>
-      <c r="P9" s="93" t="s">
+      <c r="O9" s="59"/>
+      <c r="P9" s="62" t="s">
         <v>25</v>
       </c>
-      <c r="Q9" s="58"/>
-    </row>
-    <row r="10" spans="2:17" x14ac:dyDescent="0.25">
+      <c r="Q9" s="59"/>
+    </row>
+    <row r="10" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B10" s="4">
         <v>3</v>
       </c>
-      <c r="C10" s="53"/>
+      <c r="C10" s="61"/>
       <c r="D10" s="4" t="s">
         <v>86</v>
       </c>
@@ -2009,20 +2030,20 @@
       <c r="M10" s="14" t="s">
         <v>21</v>
       </c>
-      <c r="N10" s="94" t="s">
+      <c r="N10" s="69" t="s">
         <v>84</v>
       </c>
-      <c r="O10" s="58"/>
-      <c r="P10" s="94" t="s">
+      <c r="O10" s="59"/>
+      <c r="P10" s="69" t="s">
         <v>28</v>
       </c>
-      <c r="Q10" s="58"/>
-    </row>
-    <row r="11" spans="2:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Q10" s="59"/>
+    </row>
+    <row r="11" spans="2:17" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B11" s="4">
         <v>4</v>
       </c>
-      <c r="C11" s="96"/>
+      <c r="C11" s="60"/>
       <c r="D11" s="4"/>
       <c r="E11" s="4" t="s">
         <v>87</v>
@@ -2048,18 +2069,18 @@
       <c r="M11" s="14" t="s">
         <v>21</v>
       </c>
-      <c r="N11" s="94" t="s">
+      <c r="N11" s="69" t="s">
         <v>84</v>
       </c>
-      <c r="O11" s="58"/>
-      <c r="P11" s="94" t="s">
+      <c r="O11" s="59"/>
+      <c r="P11" s="69" t="s">
         <v>31</v>
       </c>
-      <c r="Q11" s="58"/>
-    </row>
-    <row r="12" spans="2:17" x14ac:dyDescent="0.25">
+      <c r="Q11" s="59"/>
+    </row>
+    <row r="12" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B12" s="4"/>
-      <c r="C12" s="53"/>
+      <c r="C12" s="61"/>
       <c r="D12" s="4"/>
       <c r="E12" s="4"/>
       <c r="G12" s="13"/>
@@ -2071,12 +2092,12 @@
       <c r="M12" s="9"/>
       <c r="N12" s="9"/>
       <c r="O12" s="9"/>
-      <c r="P12" s="101"/>
-      <c r="Q12" s="58"/>
-    </row>
-    <row r="13" spans="2:17" x14ac:dyDescent="0.25">
+      <c r="P12" s="65"/>
+      <c r="Q12" s="59"/>
+    </row>
+    <row r="13" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B13" s="4"/>
-      <c r="C13" s="96"/>
+      <c r="C13" s="60"/>
       <c r="D13" s="4"/>
       <c r="E13" s="4"/>
       <c r="G13" s="13"/>
@@ -2086,14 +2107,14 @@
       <c r="K13" s="9"/>
       <c r="L13" s="9"/>
       <c r="M13" s="9"/>
-      <c r="N13" s="101"/>
-      <c r="O13" s="58"/>
-      <c r="P13" s="101"/>
-      <c r="Q13" s="58"/>
-    </row>
-    <row r="14" spans="2:17" x14ac:dyDescent="0.25">
+      <c r="N13" s="65"/>
+      <c r="O13" s="59"/>
+      <c r="P13" s="65"/>
+      <c r="Q13" s="59"/>
+    </row>
+    <row r="14" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B14" s="4"/>
-      <c r="C14" s="53"/>
+      <c r="C14" s="61"/>
       <c r="D14" s="4"/>
       <c r="E14" s="4"/>
       <c r="G14" s="19"/>
@@ -2103,14 +2124,14 @@
       <c r="K14" s="18"/>
       <c r="L14" s="18"/>
       <c r="M14" s="18"/>
-      <c r="N14" s="97"/>
-      <c r="O14" s="58"/>
-      <c r="P14" s="98"/>
-      <c r="Q14" s="58"/>
-    </row>
-    <row r="15" spans="2:17" x14ac:dyDescent="0.25">
+      <c r="N14" s="71"/>
+      <c r="O14" s="59"/>
+      <c r="P14" s="63"/>
+      <c r="Q14" s="59"/>
+    </row>
+    <row r="15" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B15" s="4"/>
-      <c r="C15" s="96"/>
+      <c r="C15" s="60"/>
       <c r="D15" s="4"/>
       <c r="E15" s="4"/>
       <c r="G15" s="19"/>
@@ -2120,14 +2141,14 @@
       <c r="K15" s="18"/>
       <c r="L15" s="18"/>
       <c r="M15" s="18"/>
-      <c r="N15" s="93"/>
-      <c r="O15" s="58"/>
-      <c r="P15" s="98"/>
-      <c r="Q15" s="58"/>
-    </row>
-    <row r="16" spans="2:17" x14ac:dyDescent="0.25">
+      <c r="N15" s="62"/>
+      <c r="O15" s="59"/>
+      <c r="P15" s="63"/>
+      <c r="Q15" s="59"/>
+    </row>
+    <row r="16" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B16" s="4"/>
-      <c r="C16" s="53"/>
+      <c r="C16" s="61"/>
       <c r="D16" s="4"/>
       <c r="E16" s="4"/>
       <c r="G16" s="19"/>
@@ -2137,14 +2158,14 @@
       <c r="K16" s="18"/>
       <c r="L16" s="18"/>
       <c r="M16" s="18"/>
-      <c r="N16" s="93"/>
-      <c r="O16" s="58"/>
-      <c r="P16" s="98"/>
-      <c r="Q16" s="58"/>
-    </row>
-    <row r="17" spans="2:17" x14ac:dyDescent="0.25">
+      <c r="N16" s="62"/>
+      <c r="O16" s="59"/>
+      <c r="P16" s="63"/>
+      <c r="Q16" s="59"/>
+    </row>
+    <row r="17" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B17" s="4"/>
-      <c r="C17" s="96"/>
+      <c r="C17" s="60"/>
       <c r="D17" s="4"/>
       <c r="E17" s="4"/>
       <c r="G17" s="19"/>
@@ -2154,14 +2175,14 @@
       <c r="K17" s="18"/>
       <c r="L17" s="18"/>
       <c r="M17" s="18"/>
-      <c r="N17" s="93"/>
-      <c r="O17" s="58"/>
-      <c r="P17" s="98"/>
-      <c r="Q17" s="58"/>
-    </row>
-    <row r="18" spans="2:17" x14ac:dyDescent="0.25">
+      <c r="N17" s="62"/>
+      <c r="O17" s="59"/>
+      <c r="P17" s="63"/>
+      <c r="Q17" s="59"/>
+    </row>
+    <row r="18" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B18" s="4"/>
-      <c r="C18" s="53"/>
+      <c r="C18" s="61"/>
       <c r="D18" s="4"/>
       <c r="E18" s="4"/>
       <c r="G18" s="19"/>
@@ -2171,14 +2192,14 @@
       <c r="K18" s="18"/>
       <c r="L18" s="18"/>
       <c r="M18" s="18"/>
-      <c r="N18" s="93"/>
-      <c r="O18" s="58"/>
-      <c r="P18" s="98"/>
-      <c r="Q18" s="58"/>
-    </row>
-    <row r="19" spans="2:17" x14ac:dyDescent="0.25">
+      <c r="N18" s="62"/>
+      <c r="O18" s="59"/>
+      <c r="P18" s="63"/>
+      <c r="Q18" s="59"/>
+    </row>
+    <row r="19" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B19" s="4"/>
-      <c r="C19" s="96"/>
+      <c r="C19" s="60"/>
       <c r="D19" s="4"/>
       <c r="E19" s="4"/>
       <c r="G19" s="23"/>
@@ -2188,23 +2209,48 @@
       <c r="K19" s="2"/>
       <c r="L19" s="2"/>
       <c r="M19" s="2"/>
-      <c r="N19" s="93"/>
-      <c r="O19" s="58"/>
-      <c r="P19" s="98"/>
-      <c r="Q19" s="58"/>
-    </row>
-    <row r="20" spans="2:17" x14ac:dyDescent="0.25">
+      <c r="N19" s="62"/>
+      <c r="O19" s="59"/>
+      <c r="P19" s="63"/>
+      <c r="Q19" s="59"/>
+    </row>
+    <row r="20" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B20" s="4"/>
-      <c r="C20" s="53"/>
+      <c r="C20" s="61"/>
       <c r="D20" s="4"/>
       <c r="E20" s="4"/>
     </row>
-    <row r="22" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="F22" s="99"/>
-      <c r="G22" s="66"/>
+    <row r="22" spans="2:17" x14ac:dyDescent="0.3">
+      <c r="F22" s="66"/>
+      <c r="G22" s="67"/>
     </row>
   </sheetData>
   <mergeCells count="41">
+    <mergeCell ref="N16:O16"/>
+    <mergeCell ref="P10:Q10"/>
+    <mergeCell ref="H6:H7"/>
+    <mergeCell ref="C9:C10"/>
+    <mergeCell ref="P6:Q6"/>
+    <mergeCell ref="P8:Q8"/>
+    <mergeCell ref="G6:G7"/>
+    <mergeCell ref="N11:O11"/>
+    <mergeCell ref="N7:O7"/>
+    <mergeCell ref="F22:G22"/>
+    <mergeCell ref="G5:Q5"/>
+    <mergeCell ref="N19:O19"/>
+    <mergeCell ref="P13:Q13"/>
+    <mergeCell ref="P19:Q19"/>
+    <mergeCell ref="N13:O13"/>
+    <mergeCell ref="N18:O18"/>
+    <mergeCell ref="P11:Q11"/>
+    <mergeCell ref="I6:O6"/>
+    <mergeCell ref="N8:O8"/>
+    <mergeCell ref="N14:O14"/>
+    <mergeCell ref="N17:O17"/>
+    <mergeCell ref="P17:Q17"/>
+    <mergeCell ref="P7:Q7"/>
+    <mergeCell ref="P16:Q16"/>
+    <mergeCell ref="N10:O10"/>
     <mergeCell ref="B3:G3"/>
     <mergeCell ref="C19:C20"/>
     <mergeCell ref="N9:O9"/>
@@ -2215,37 +2261,12 @@
     <mergeCell ref="P15:Q15"/>
     <mergeCell ref="C15:C16"/>
     <mergeCell ref="P14:Q14"/>
-    <mergeCell ref="F22:G22"/>
-    <mergeCell ref="G5:Q5"/>
-    <mergeCell ref="N19:O19"/>
-    <mergeCell ref="P13:Q13"/>
-    <mergeCell ref="P19:Q19"/>
-    <mergeCell ref="N13:O13"/>
-    <mergeCell ref="N18:O18"/>
-    <mergeCell ref="P11:Q11"/>
     <mergeCell ref="C11:C12"/>
-    <mergeCell ref="I6:O6"/>
-    <mergeCell ref="N8:O8"/>
-    <mergeCell ref="N14:O14"/>
-    <mergeCell ref="N17:O17"/>
-    <mergeCell ref="P17:Q17"/>
-    <mergeCell ref="P7:Q7"/>
     <mergeCell ref="C17:C18"/>
-    <mergeCell ref="P16:Q16"/>
     <mergeCell ref="C7:C8"/>
-    <mergeCell ref="N10:O10"/>
     <mergeCell ref="C13:C14"/>
     <mergeCell ref="B5:E5"/>
     <mergeCell ref="P9:Q9"/>
-    <mergeCell ref="C9:C10"/>
-    <mergeCell ref="P6:Q6"/>
-    <mergeCell ref="P8:Q8"/>
-    <mergeCell ref="G6:G7"/>
-    <mergeCell ref="N11:O11"/>
-    <mergeCell ref="N7:O7"/>
-    <mergeCell ref="N16:O16"/>
-    <mergeCell ref="P10:Q10"/>
-    <mergeCell ref="H6:H7"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2257,67 +2278,67 @@
     <tabColor theme="9" tint="0.59999389629810485"/>
   </sheetPr>
   <dimension ref="B1:R29"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="11.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.5703125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="30.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.5546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="30.109375" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="7" customWidth="1"/>
-    <col min="6" max="6" width="5.5703125" customWidth="1"/>
-    <col min="7" max="7" width="9.42578125" customWidth="1"/>
+    <col min="6" max="6" width="5.5546875" customWidth="1"/>
+    <col min="7" max="7" width="9.44140625" customWidth="1"/>
     <col min="9" max="9" width="10" customWidth="1"/>
-    <col min="10" max="10" width="10.140625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="9.5703125" customWidth="1"/>
-    <col min="12" max="12" width="18.28515625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="7.28515625" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="12.85546875" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="8.85546875" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="18.140625" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="23.28515625" customWidth="1"/>
-    <col min="18" max="18" width="9.42578125" customWidth="1"/>
+    <col min="10" max="10" width="10.109375" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="9.5546875" customWidth="1"/>
+    <col min="12" max="12" width="18.33203125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="7.33203125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="12.88671875" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="8.88671875" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="18.109375" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="23.33203125" customWidth="1"/>
+    <col min="18" max="18" width="9.44140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B1" s="89" t="s">
+    <row r="1" spans="2:18" x14ac:dyDescent="0.3">
+      <c r="B1" s="64" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="77"/>
-      <c r="D1" s="77"/>
-      <c r="E1" s="58"/>
-    </row>
-    <row r="3" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B3" s="102" t="s">
+      <c r="C1" s="58"/>
+      <c r="D1" s="58"/>
+      <c r="E1" s="59"/>
+    </row>
+    <row r="3" spans="2:18" x14ac:dyDescent="0.3">
+      <c r="B3" s="57" t="s">
         <v>72</v>
       </c>
-      <c r="C3" s="77"/>
-      <c r="D3" s="77"/>
-      <c r="E3" s="77"/>
-      <c r="F3" s="77"/>
-      <c r="G3" s="58"/>
-    </row>
-    <row r="5" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B5" s="107" t="s">
+      <c r="C3" s="58"/>
+      <c r="D3" s="58"/>
+      <c r="E3" s="58"/>
+      <c r="F3" s="58"/>
+      <c r="G3" s="59"/>
+    </row>
+    <row r="5" spans="2:18" x14ac:dyDescent="0.3">
+      <c r="B5" s="80" t="s">
         <v>91</v>
       </c>
-      <c r="C5" s="77"/>
-      <c r="D5" s="58"/>
+      <c r="C5" s="58"/>
+      <c r="D5" s="59"/>
       <c r="E5" s="3"/>
-      <c r="G5" s="100" t="s">
+      <c r="G5" s="68" t="s">
         <v>92</v>
       </c>
-      <c r="H5" s="77"/>
-      <c r="I5" s="77"/>
-      <c r="J5" s="77"/>
-      <c r="K5" s="77"/>
-      <c r="L5" s="77"/>
-      <c r="M5" s="77"/>
-      <c r="N5" s="77"/>
-      <c r="O5" s="77"/>
-      <c r="P5" s="77"/>
-      <c r="Q5" s="77"/>
-      <c r="R5" s="58"/>
-    </row>
-    <row r="6" spans="2:18" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H5" s="58"/>
+      <c r="I5" s="58"/>
+      <c r="J5" s="58"/>
+      <c r="K5" s="58"/>
+      <c r="L5" s="58"/>
+      <c r="M5" s="58"/>
+      <c r="N5" s="58"/>
+      <c r="O5" s="58"/>
+      <c r="P5" s="58"/>
+      <c r="Q5" s="58"/>
+      <c r="R5" s="59"/>
+    </row>
+    <row r="6" spans="2:18" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B6" s="4" t="s">
         <v>93</v>
       </c>
@@ -2328,45 +2349,45 @@
         <v>91</v>
       </c>
       <c r="E6" s="10"/>
-      <c r="G6" s="52" t="s">
+      <c r="G6" s="73" t="s">
         <v>94</v>
       </c>
-      <c r="H6" s="52" t="s">
+      <c r="H6" s="73" t="s">
         <v>95</v>
       </c>
-      <c r="I6" s="52" t="s">
+      <c r="I6" s="73" t="s">
         <v>96</v>
       </c>
-      <c r="J6" s="76" t="s">
+      <c r="J6" s="70" t="s">
         <v>97</v>
       </c>
-      <c r="K6" s="108" t="s">
+      <c r="K6" s="81" t="s">
         <v>6</v>
       </c>
-      <c r="L6" s="77"/>
-      <c r="M6" s="77"/>
-      <c r="N6" s="77"/>
-      <c r="O6" s="77"/>
-      <c r="P6" s="58"/>
-      <c r="Q6" s="108" t="s">
+      <c r="L6" s="58"/>
+      <c r="M6" s="58"/>
+      <c r="N6" s="58"/>
+      <c r="O6" s="58"/>
+      <c r="P6" s="59"/>
+      <c r="Q6" s="81" t="s">
         <v>7</v>
       </c>
-      <c r="R6" s="58"/>
-    </row>
-    <row r="7" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B7" s="113">
+      <c r="R6" s="59"/>
+    </row>
+    <row r="7" spans="2:18" x14ac:dyDescent="0.3">
+      <c r="B7" s="56">
         <v>1</v>
       </c>
-      <c r="C7" s="111" t="s">
+      <c r="C7" s="53" t="s">
         <v>99</v>
       </c>
       <c r="D7" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="G7" s="53"/>
-      <c r="H7" s="53"/>
-      <c r="I7" s="53"/>
-      <c r="J7" s="53"/>
+      <c r="G7" s="61"/>
+      <c r="H7" s="61"/>
+      <c r="I7" s="61"/>
+      <c r="J7" s="61"/>
       <c r="K7" s="23" t="s">
         <v>8</v>
       </c>
@@ -2385,14 +2406,14 @@
       <c r="P7" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="Q7" s="76" t="s">
+      <c r="Q7" s="70" t="s">
         <v>98</v>
       </c>
-      <c r="R7" s="58"/>
-    </row>
-    <row r="8" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B8" s="114"/>
-      <c r="C8" s="112"/>
+      <c r="R7" s="59"/>
+    </row>
+    <row r="8" spans="2:18" x14ac:dyDescent="0.3">
+      <c r="B8" s="52"/>
+      <c r="C8" s="54"/>
       <c r="D8" s="2" t="s">
         <v>102</v>
       </c>
@@ -2424,16 +2445,16 @@
       <c r="P8" s="34" t="s">
         <v>84</v>
       </c>
-      <c r="Q8" s="103" t="s">
+      <c r="Q8" s="75" t="s">
         <v>25</v>
       </c>
-      <c r="R8" s="58"/>
-    </row>
-    <row r="9" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B9" s="113">
+      <c r="R8" s="59"/>
+    </row>
+    <row r="9" spans="2:18" x14ac:dyDescent="0.3">
+      <c r="B9" s="56">
         <v>2</v>
       </c>
-      <c r="C9" s="111" t="s">
+      <c r="C9" s="53" t="s">
         <v>85</v>
       </c>
       <c r="D9" s="2" t="s">
@@ -2469,14 +2490,14 @@
       <c r="P9" s="18" t="s">
         <v>84</v>
       </c>
-      <c r="Q9" s="101" t="s">
+      <c r="Q9" s="65" t="s">
         <v>23</v>
       </c>
-      <c r="R9" s="58"/>
-    </row>
-    <row r="10" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B10" s="114"/>
-      <c r="C10" s="112"/>
+      <c r="R9" s="59"/>
+    </row>
+    <row r="10" spans="2:18" x14ac:dyDescent="0.3">
+      <c r="B10" s="52"/>
+      <c r="C10" s="54"/>
       <c r="D10" s="2" t="s">
         <v>104</v>
       </c>
@@ -2510,14 +2531,14 @@
       <c r="P10" s="34" t="s">
         <v>84</v>
       </c>
-      <c r="Q10" s="103" t="s">
+      <c r="Q10" s="75" t="s">
         <v>28</v>
       </c>
-      <c r="R10" s="58"/>
-    </row>
-    <row r="11" spans="2:18" x14ac:dyDescent="0.25">
+      <c r="R10" s="59"/>
+    </row>
+    <row r="11" spans="2:18" x14ac:dyDescent="0.3">
       <c r="B11" s="2"/>
-      <c r="C11" s="110"/>
+      <c r="C11" s="55"/>
       <c r="D11" s="2"/>
       <c r="G11" s="23" t="s">
         <v>37</v>
@@ -2549,14 +2570,14 @@
       <c r="P11" s="34" t="s">
         <v>84</v>
       </c>
-      <c r="Q11" s="103" t="s">
+      <c r="Q11" s="75" t="s">
         <v>23</v>
       </c>
-      <c r="R11" s="58"/>
-    </row>
-    <row r="12" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B12" s="96"/>
-      <c r="C12" s="96"/>
+      <c r="R11" s="59"/>
+    </row>
+    <row r="12" spans="2:18" x14ac:dyDescent="0.3">
+      <c r="B12" s="60"/>
+      <c r="C12" s="60"/>
       <c r="D12" s="2"/>
       <c r="G12" s="23"/>
       <c r="H12" s="17"/>
@@ -2568,12 +2589,12 @@
       <c r="N12" s="34"/>
       <c r="O12" s="34"/>
       <c r="P12" s="34"/>
-      <c r="Q12" s="103"/>
-      <c r="R12" s="58"/>
-    </row>
-    <row r="13" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B13" s="104"/>
-      <c r="C13" s="104"/>
+      <c r="Q12" s="75"/>
+      <c r="R12" s="59"/>
+    </row>
+    <row r="13" spans="2:18" x14ac:dyDescent="0.3">
+      <c r="B13" s="77"/>
+      <c r="C13" s="77"/>
       <c r="D13" s="2"/>
       <c r="G13" s="19"/>
       <c r="H13" s="20"/>
@@ -2585,12 +2606,12 @@
       <c r="N13" s="18"/>
       <c r="O13" s="18"/>
       <c r="P13" s="18"/>
-      <c r="Q13" s="101"/>
-      <c r="R13" s="58"/>
-    </row>
-    <row r="14" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B14" s="104"/>
-      <c r="C14" s="104"/>
+      <c r="Q13" s="65"/>
+      <c r="R13" s="59"/>
+    </row>
+    <row r="14" spans="2:18" x14ac:dyDescent="0.3">
+      <c r="B14" s="77"/>
+      <c r="C14" s="77"/>
       <c r="D14" s="2"/>
       <c r="G14" s="23"/>
       <c r="H14" s="17"/>
@@ -2602,12 +2623,12 @@
       <c r="N14" s="34"/>
       <c r="O14" s="34"/>
       <c r="P14" s="34"/>
-      <c r="Q14" s="103"/>
-      <c r="R14" s="58"/>
-    </row>
-    <row r="15" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B15" s="104"/>
-      <c r="C15" s="104"/>
+      <c r="Q14" s="75"/>
+      <c r="R14" s="59"/>
+    </row>
+    <row r="15" spans="2:18" x14ac:dyDescent="0.3">
+      <c r="B15" s="77"/>
+      <c r="C15" s="77"/>
       <c r="D15" s="2"/>
       <c r="G15" s="23"/>
       <c r="H15" s="17"/>
@@ -2619,12 +2640,12 @@
       <c r="N15" s="34"/>
       <c r="O15" s="34"/>
       <c r="P15" s="34"/>
-      <c r="Q15" s="103"/>
-      <c r="R15" s="58"/>
-    </row>
-    <row r="16" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B16" s="104"/>
-      <c r="C16" s="104"/>
+      <c r="Q15" s="75"/>
+      <c r="R15" s="59"/>
+    </row>
+    <row r="16" spans="2:18" x14ac:dyDescent="0.3">
+      <c r="B16" s="77"/>
+      <c r="C16" s="77"/>
       <c r="D16" s="2"/>
       <c r="G16" s="23"/>
       <c r="H16" s="17"/>
@@ -2636,12 +2657,12 @@
       <c r="N16" s="34"/>
       <c r="O16" s="34"/>
       <c r="P16" s="34"/>
-      <c r="Q16" s="103"/>
-      <c r="R16" s="58"/>
-    </row>
-    <row r="17" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B17" s="53"/>
-      <c r="C17" s="53"/>
+      <c r="Q16" s="75"/>
+      <c r="R16" s="59"/>
+    </row>
+    <row r="17" spans="2:18" x14ac:dyDescent="0.3">
+      <c r="B17" s="61"/>
+      <c r="C17" s="61"/>
       <c r="D17" s="2"/>
       <c r="G17" s="23"/>
       <c r="H17" s="17"/>
@@ -2653,12 +2674,12 @@
       <c r="N17" s="34"/>
       <c r="O17" s="34"/>
       <c r="P17" s="34"/>
-      <c r="Q17" s="103"/>
-      <c r="R17" s="58"/>
-    </row>
-    <row r="18" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B18" s="96"/>
-      <c r="C18" s="105"/>
+      <c r="Q17" s="75"/>
+      <c r="R17" s="59"/>
+    </row>
+    <row r="18" spans="2:18" x14ac:dyDescent="0.3">
+      <c r="B18" s="60"/>
+      <c r="C18" s="78"/>
       <c r="D18" s="2"/>
       <c r="G18" s="23"/>
       <c r="H18" s="17"/>
@@ -2670,12 +2691,12 @@
       <c r="N18" s="34"/>
       <c r="O18" s="34"/>
       <c r="P18" s="34"/>
-      <c r="Q18" s="103"/>
-      <c r="R18" s="58"/>
-    </row>
-    <row r="19" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B19" s="104"/>
-      <c r="C19" s="104"/>
+      <c r="Q18" s="75"/>
+      <c r="R18" s="59"/>
+    </row>
+    <row r="19" spans="2:18" x14ac:dyDescent="0.3">
+      <c r="B19" s="77"/>
+      <c r="C19" s="77"/>
       <c r="D19" s="2"/>
       <c r="G19" s="23"/>
       <c r="H19" s="17"/>
@@ -2687,12 +2708,12 @@
       <c r="N19" s="34"/>
       <c r="O19" s="34"/>
       <c r="P19" s="34"/>
-      <c r="Q19" s="103"/>
-      <c r="R19" s="58"/>
-    </row>
-    <row r="20" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B20" s="104"/>
-      <c r="C20" s="104"/>
+      <c r="Q19" s="75"/>
+      <c r="R19" s="59"/>
+    </row>
+    <row r="20" spans="2:18" x14ac:dyDescent="0.3">
+      <c r="B20" s="77"/>
+      <c r="C20" s="77"/>
       <c r="D20" s="2"/>
       <c r="G20" s="23"/>
       <c r="H20" s="17"/>
@@ -2704,12 +2725,12 @@
       <c r="N20" s="34"/>
       <c r="O20" s="34"/>
       <c r="P20" s="34"/>
-      <c r="Q20" s="103"/>
-      <c r="R20" s="58"/>
-    </row>
-    <row r="21" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B21" s="104"/>
-      <c r="C21" s="104"/>
+      <c r="Q20" s="75"/>
+      <c r="R20" s="59"/>
+    </row>
+    <row r="21" spans="2:18" x14ac:dyDescent="0.3">
+      <c r="B21" s="77"/>
+      <c r="C21" s="77"/>
       <c r="D21" s="2"/>
       <c r="G21" s="23"/>
       <c r="H21" s="17"/>
@@ -2721,12 +2742,12 @@
       <c r="N21" s="34"/>
       <c r="O21" s="34"/>
       <c r="P21" s="34"/>
-      <c r="Q21" s="103"/>
-      <c r="R21" s="58"/>
-    </row>
-    <row r="22" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B22" s="104"/>
-      <c r="C22" s="104"/>
+      <c r="Q21" s="75"/>
+      <c r="R21" s="59"/>
+    </row>
+    <row r="22" spans="2:18" x14ac:dyDescent="0.3">
+      <c r="B22" s="77"/>
+      <c r="C22" s="77"/>
       <c r="D22" s="2"/>
       <c r="G22" s="23"/>
       <c r="H22" s="17"/>
@@ -2738,12 +2759,12 @@
       <c r="N22" s="34"/>
       <c r="O22" s="34"/>
       <c r="P22" s="34"/>
-      <c r="Q22" s="103"/>
-      <c r="R22" s="58"/>
-    </row>
-    <row r="23" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B23" s="53"/>
-      <c r="C23" s="53"/>
+      <c r="Q22" s="75"/>
+      <c r="R22" s="59"/>
+    </row>
+    <row r="23" spans="2:18" x14ac:dyDescent="0.3">
+      <c r="B23" s="61"/>
+      <c r="C23" s="61"/>
       <c r="D23" s="2"/>
       <c r="G23" s="23"/>
       <c r="H23" s="17"/>
@@ -2755,12 +2776,12 @@
       <c r="N23" s="34"/>
       <c r="O23" s="34"/>
       <c r="P23" s="34"/>
-      <c r="Q23" s="103"/>
-      <c r="R23" s="58"/>
-    </row>
-    <row r="24" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B24" s="96"/>
-      <c r="C24" s="105"/>
+      <c r="Q23" s="75"/>
+      <c r="R23" s="59"/>
+    </row>
+    <row r="24" spans="2:18" x14ac:dyDescent="0.3">
+      <c r="B24" s="60"/>
+      <c r="C24" s="78"/>
       <c r="D24" s="2"/>
       <c r="G24" s="23"/>
       <c r="H24" s="17"/>
@@ -2772,12 +2793,12 @@
       <c r="N24" s="34"/>
       <c r="O24" s="34"/>
       <c r="P24" s="34"/>
-      <c r="Q24" s="103"/>
-      <c r="R24" s="58"/>
-    </row>
-    <row r="25" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B25" s="104"/>
-      <c r="C25" s="104"/>
+      <c r="Q24" s="75"/>
+      <c r="R24" s="59"/>
+    </row>
+    <row r="25" spans="2:18" x14ac:dyDescent="0.3">
+      <c r="B25" s="77"/>
+      <c r="C25" s="77"/>
       <c r="D25" s="2"/>
       <c r="G25" s="23"/>
       <c r="H25" s="17"/>
@@ -2789,45 +2810,67 @@
       <c r="N25" s="34"/>
       <c r="O25" s="34"/>
       <c r="P25" s="34"/>
-      <c r="Q25" s="103"/>
-      <c r="R25" s="58"/>
-    </row>
-    <row r="26" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B26" s="104"/>
-      <c r="C26" s="104"/>
+      <c r="Q25" s="75"/>
+      <c r="R25" s="59"/>
+    </row>
+    <row r="26" spans="2:18" x14ac:dyDescent="0.3">
+      <c r="B26" s="77"/>
+      <c r="C26" s="77"/>
       <c r="D26" s="2"/>
     </row>
-    <row r="27" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B27" s="104"/>
-      <c r="C27" s="104"/>
+    <row r="27" spans="2:18" x14ac:dyDescent="0.3">
+      <c r="B27" s="77"/>
+      <c r="C27" s="77"/>
       <c r="D27" s="2"/>
     </row>
-    <row r="28" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B28" s="104"/>
-      <c r="C28" s="104"/>
+    <row r="28" spans="2:18" x14ac:dyDescent="0.3">
+      <c r="B28" s="77"/>
+      <c r="C28" s="77"/>
       <c r="D28" s="2"/>
-      <c r="G28" s="99"/>
-      <c r="H28" s="66"/>
-      <c r="I28" s="106"/>
-      <c r="J28" s="66"/>
-      <c r="K28" s="66"/>
-      <c r="L28" s="66"/>
-      <c r="M28" s="66"/>
+      <c r="G28" s="66"/>
+      <c r="H28" s="67"/>
+      <c r="I28" s="79"/>
+      <c r="J28" s="67"/>
+      <c r="K28" s="67"/>
+      <c r="L28" s="67"/>
+      <c r="M28" s="67"/>
       <c r="N28" s="43"/>
     </row>
-    <row r="29" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B29" s="53"/>
-      <c r="C29" s="53"/>
+    <row r="29" spans="2:18" x14ac:dyDescent="0.3">
+      <c r="B29" s="61"/>
+      <c r="C29" s="61"/>
       <c r="D29" s="2"/>
-      <c r="I29" s="109"/>
-      <c r="J29" s="66"/>
-      <c r="K29" s="66"/>
-      <c r="L29" s="66"/>
-      <c r="M29" s="66"/>
+      <c r="I29" s="76"/>
+      <c r="J29" s="67"/>
+      <c r="K29" s="67"/>
+      <c r="L29" s="67"/>
+      <c r="M29" s="67"/>
       <c r="N29" s="44"/>
     </row>
   </sheetData>
   <mergeCells count="38">
+    <mergeCell ref="Q22:R22"/>
+    <mergeCell ref="B24:B29"/>
+    <mergeCell ref="H6:H7"/>
+    <mergeCell ref="Q24:R24"/>
+    <mergeCell ref="J6:J7"/>
+    <mergeCell ref="Q18:R18"/>
+    <mergeCell ref="Q8:R8"/>
+    <mergeCell ref="Q23:R23"/>
+    <mergeCell ref="Q9:R9"/>
+    <mergeCell ref="B18:B23"/>
+    <mergeCell ref="C18:C23"/>
+    <mergeCell ref="Q16:R16"/>
+    <mergeCell ref="Q13:R13"/>
+    <mergeCell ref="Q7:R7"/>
+    <mergeCell ref="Q25:R25"/>
+    <mergeCell ref="Q21:R21"/>
+    <mergeCell ref="B5:D5"/>
+    <mergeCell ref="B12:B17"/>
+    <mergeCell ref="Q15:R15"/>
+    <mergeCell ref="Q6:R6"/>
+    <mergeCell ref="K6:P6"/>
+    <mergeCell ref="Q12:R12"/>
     <mergeCell ref="B3:G3"/>
     <mergeCell ref="B1:E1"/>
     <mergeCell ref="Q17:R17"/>
@@ -2844,28 +2887,6 @@
     <mergeCell ref="G28:H28"/>
     <mergeCell ref="I28:M28"/>
     <mergeCell ref="Q19:R19"/>
-    <mergeCell ref="B5:D5"/>
-    <mergeCell ref="B12:B17"/>
-    <mergeCell ref="Q15:R15"/>
-    <mergeCell ref="Q6:R6"/>
-    <mergeCell ref="K6:P6"/>
-    <mergeCell ref="Q22:R22"/>
-    <mergeCell ref="B24:B29"/>
-    <mergeCell ref="H6:H7"/>
-    <mergeCell ref="Q24:R24"/>
-    <mergeCell ref="J6:J7"/>
-    <mergeCell ref="Q18:R18"/>
-    <mergeCell ref="Q8:R8"/>
-    <mergeCell ref="Q23:R23"/>
-    <mergeCell ref="Q9:R9"/>
-    <mergeCell ref="B18:B23"/>
-    <mergeCell ref="C18:C23"/>
-    <mergeCell ref="Q16:R16"/>
-    <mergeCell ref="Q13:R13"/>
-    <mergeCell ref="Q7:R7"/>
-    <mergeCell ref="Q25:R25"/>
-    <mergeCell ref="Q21:R21"/>
-    <mergeCell ref="Q12:R12"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -2879,75 +2900,75 @@
     <tabColor theme="7" tint="-0.249977111117893"/>
   </sheetPr>
   <dimension ref="B1:P21"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="6" max="6" width="12.140625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="17.5703125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="10.5703125" customWidth="1"/>
-    <col min="9" max="9" width="13.140625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="8.85546875" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="9.85546875" customWidth="1"/>
-    <col min="13" max="13" width="30.28515625" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="10.85546875" customWidth="1"/>
+    <col min="6" max="6" width="12.109375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="17.5546875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.5546875" customWidth="1"/>
+    <col min="9" max="9" width="13.109375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="8.88671875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="9.88671875" customWidth="1"/>
+    <col min="13" max="13" width="30.33203125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="10.88671875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B1" s="89" t="s">
+    <row r="1" spans="2:14" x14ac:dyDescent="0.3">
+      <c r="B1" s="64" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="77"/>
-      <c r="D1" s="77"/>
-      <c r="E1" s="58"/>
-    </row>
-    <row r="3" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B3" s="83" t="s">
+      <c r="C1" s="58"/>
+      <c r="D1" s="58"/>
+      <c r="E1" s="59"/>
+    </row>
+    <row r="3" spans="2:14" x14ac:dyDescent="0.3">
+      <c r="B3" s="96" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="77"/>
-      <c r="D3" s="77"/>
-      <c r="E3" s="77"/>
-      <c r="F3" s="77"/>
-      <c r="G3" s="77"/>
-      <c r="H3" s="77"/>
-      <c r="I3" s="77"/>
-      <c r="J3" s="77"/>
-      <c r="K3" s="77"/>
-      <c r="L3" s="77"/>
-      <c r="M3" s="77"/>
-      <c r="N3" s="58"/>
-    </row>
-    <row r="4" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B4" s="90" t="s">
+      <c r="C3" s="58"/>
+      <c r="D3" s="58"/>
+      <c r="E3" s="58"/>
+      <c r="F3" s="58"/>
+      <c r="G3" s="58"/>
+      <c r="H3" s="58"/>
+      <c r="I3" s="58"/>
+      <c r="J3" s="58"/>
+      <c r="K3" s="58"/>
+      <c r="L3" s="58"/>
+      <c r="M3" s="58"/>
+      <c r="N3" s="59"/>
+    </row>
+    <row r="4" spans="2:14" x14ac:dyDescent="0.3">
+      <c r="B4" s="85" t="s">
         <v>2</v>
       </c>
-      <c r="C4" s="59" t="s">
+      <c r="C4" s="104" t="s">
         <v>3</v>
       </c>
-      <c r="D4" s="74" t="s">
+      <c r="D4" s="113" t="s">
         <v>4</v>
       </c>
-      <c r="E4" s="63" t="s">
+      <c r="E4" s="108" t="s">
         <v>5</v>
       </c>
-      <c r="F4" s="76" t="s">
+      <c r="F4" s="70" t="s">
         <v>6</v>
       </c>
-      <c r="G4" s="77"/>
-      <c r="H4" s="77"/>
-      <c r="I4" s="77"/>
-      <c r="J4" s="77"/>
-      <c r="K4" s="77"/>
-      <c r="L4" s="58"/>
-      <c r="M4" s="76" t="s">
+      <c r="G4" s="58"/>
+      <c r="H4" s="58"/>
+      <c r="I4" s="58"/>
+      <c r="J4" s="58"/>
+      <c r="K4" s="58"/>
+      <c r="L4" s="59"/>
+      <c r="M4" s="70" t="s">
         <v>7</v>
       </c>
-      <c r="N4" s="58"/>
-    </row>
-    <row r="5" spans="2:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B5" s="64"/>
-      <c r="C5" s="60"/>
-      <c r="D5" s="75"/>
-      <c r="E5" s="64"/>
+      <c r="N4" s="59"/>
+    </row>
+    <row r="5" spans="2:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B5" s="86"/>
+      <c r="C5" s="105"/>
+      <c r="D5" s="114"/>
+      <c r="E5" s="86"/>
       <c r="F5" s="26" t="s">
         <v>8</v>
       </c>
@@ -2963,10 +2984,10 @@
       <c r="J5" s="26" t="s">
         <v>12</v>
       </c>
-      <c r="K5" s="63" t="s">
+      <c r="K5" s="108" t="s">
         <v>13</v>
       </c>
-      <c r="L5" s="68"/>
+      <c r="L5" s="95"/>
       <c r="M5" s="26" t="s">
         <v>14</v>
       </c>
@@ -2974,11 +2995,11 @@
         <v>15</v>
       </c>
     </row>
-    <row r="6" spans="2:14" ht="15.75" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:14" ht="15.75" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
       <c r="B6" s="24">
         <v>1</v>
       </c>
-      <c r="C6" s="69" t="s">
+      <c r="C6" s="111" t="s">
         <v>16</v>
       </c>
       <c r="D6" s="30" t="s">
@@ -3002,10 +3023,10 @@
       <c r="J6" s="29" t="s">
         <v>21</v>
       </c>
-      <c r="K6" s="91" t="s">
+      <c r="K6" s="88" t="s">
         <v>22</v>
       </c>
-      <c r="L6" s="81"/>
+      <c r="L6" s="89"/>
       <c r="M6" s="29" t="s">
         <v>23</v>
       </c>
@@ -3013,11 +3034,11 @@
         <v>18</v>
       </c>
     </row>
-    <row r="7" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B7" s="12">
         <v>2</v>
       </c>
-      <c r="C7" s="70"/>
+      <c r="C7" s="112"/>
       <c r="D7" s="31" t="s">
         <v>24</v>
       </c>
@@ -3037,10 +3058,10 @@
       <c r="J7" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="K7" s="88" t="s">
+      <c r="K7" s="84" t="s">
         <v>22</v>
       </c>
-      <c r="L7" s="58"/>
+      <c r="L7" s="59"/>
       <c r="M7" s="8" t="s">
         <v>25</v>
       </c>
@@ -3048,11 +3069,11 @@
         <v>18</v>
       </c>
     </row>
-    <row r="8" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B8" s="12">
         <v>3</v>
       </c>
-      <c r="C8" s="70"/>
+      <c r="C8" s="112"/>
       <c r="D8" s="31" t="s">
         <v>26</v>
       </c>
@@ -3085,11 +3106,11 @@
         <v>18</v>
       </c>
     </row>
-    <row r="9" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B9" s="12">
         <v>4</v>
       </c>
-      <c r="C9" s="70"/>
+      <c r="C9" s="112"/>
       <c r="D9" s="31" t="s">
         <v>29</v>
       </c>
@@ -3111,10 +3132,10 @@
       <c r="J9" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="K9" s="67" t="s">
+      <c r="K9" s="110" t="s">
         <v>22</v>
       </c>
-      <c r="L9" s="58"/>
+      <c r="L9" s="59"/>
       <c r="M9" s="12" t="s">
         <v>31</v>
       </c>
@@ -3122,11 +3143,11 @@
         <v>18</v>
       </c>
     </row>
-    <row r="10" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B10" s="12">
         <v>5</v>
       </c>
-      <c r="C10" s="70"/>
+      <c r="C10" s="112"/>
       <c r="D10" s="31" t="s">
         <v>18</v>
       </c>
@@ -3146,10 +3167,10 @@
       <c r="J10" s="11" t="s">
         <v>21</v>
       </c>
-      <c r="K10" s="73" t="s">
+      <c r="K10" s="87" t="s">
         <v>22</v>
       </c>
-      <c r="L10" s="58"/>
+      <c r="L10" s="59"/>
       <c r="M10" s="6" t="s">
         <v>25</v>
       </c>
@@ -3157,11 +3178,11 @@
         <v>18</v>
       </c>
     </row>
-    <row r="11" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B11" s="12">
         <v>6</v>
       </c>
-      <c r="C11" s="70"/>
+      <c r="C11" s="112"/>
       <c r="D11" s="31" t="s">
         <v>18</v>
       </c>
@@ -3183,10 +3204,10 @@
       <c r="J11" s="11" t="s">
         <v>21</v>
       </c>
-      <c r="K11" s="73" t="s">
+      <c r="K11" s="87" t="s">
         <v>22</v>
       </c>
-      <c r="L11" s="58"/>
+      <c r="L11" s="59"/>
       <c r="M11" s="5" t="s">
         <v>23</v>
       </c>
@@ -3194,11 +3215,11 @@
         <v>18</v>
       </c>
     </row>
-    <row r="12" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B12" s="12">
         <v>7</v>
       </c>
-      <c r="C12" s="70"/>
+      <c r="C12" s="112"/>
       <c r="D12" s="31" t="s">
         <v>18</v>
       </c>
@@ -3220,10 +3241,10 @@
       <c r="J12" s="11" t="s">
         <v>21</v>
       </c>
-      <c r="K12" s="73" t="s">
+      <c r="K12" s="87" t="s">
         <v>22</v>
       </c>
-      <c r="L12" s="58"/>
+      <c r="L12" s="59"/>
       <c r="M12" s="5" t="s">
         <v>28</v>
       </c>
@@ -3231,11 +3252,11 @@
         <v>18</v>
       </c>
     </row>
-    <row r="13" spans="2:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="2:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B13" s="25">
         <v>8</v>
       </c>
-      <c r="C13" s="60"/>
+      <c r="C13" s="105"/>
       <c r="D13" s="32" t="s">
         <v>18</v>
       </c>
@@ -3257,10 +3278,10 @@
       <c r="J13" s="25" t="s">
         <v>21</v>
       </c>
-      <c r="K13" s="82" t="s">
+      <c r="K13" s="94" t="s">
         <v>22</v>
       </c>
-      <c r="L13" s="68"/>
+      <c r="L13" s="95"/>
       <c r="M13" s="25" t="s">
         <v>23</v>
       </c>
@@ -3268,7 +3289,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="14" spans="2:14" ht="15.75" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:14" ht="15.75" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
       <c r="B14" s="27"/>
       <c r="C14" s="27"/>
       <c r="D14" s="28"/>
@@ -3283,7 +3304,7 @@
       <c r="M14" s="27"/>
       <c r="N14" s="27"/>
     </row>
-    <row r="15" spans="2:14" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:14" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B15" s="27" t="s">
         <v>38</v>
       </c>
@@ -3295,100 +3316,100 @@
       <c r="H15" s="7"/>
       <c r="I15" s="7"/>
       <c r="J15" s="7"/>
-      <c r="K15" s="65"/>
-      <c r="L15" s="66"/>
+      <c r="K15" s="109"/>
+      <c r="L15" s="67"/>
       <c r="M15" s="7"/>
     </row>
-    <row r="16" spans="2:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="2:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="M16" s="7"/>
     </row>
-    <row r="17" spans="2:16" ht="15.75" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="C17" s="54" t="s">
+    <row r="17" spans="2:16" ht="15.75" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
+      <c r="C17" s="99" t="s">
         <v>39</v>
       </c>
-      <c r="D17" s="55"/>
-      <c r="E17" s="55"/>
-      <c r="F17" s="56"/>
+      <c r="D17" s="100"/>
+      <c r="E17" s="100"/>
+      <c r="F17" s="101"/>
       <c r="G17" s="39" t="s">
         <v>40</v>
       </c>
-      <c r="H17" s="54" t="s">
+      <c r="H17" s="99" t="s">
         <v>41</v>
       </c>
-      <c r="I17" s="55"/>
-      <c r="J17" s="55"/>
-      <c r="K17" s="55"/>
-      <c r="L17" s="56"/>
-      <c r="M17" s="54" t="s">
+      <c r="I17" s="100"/>
+      <c r="J17" s="100"/>
+      <c r="K17" s="100"/>
+      <c r="L17" s="101"/>
+      <c r="M17" s="99" t="s">
         <v>42</v>
       </c>
-      <c r="N17" s="55"/>
-      <c r="O17" s="55"/>
-      <c r="P17" s="56"/>
-    </row>
-    <row r="18" spans="2:16" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B18" s="61" t="s">
+      <c r="N17" s="100"/>
+      <c r="O17" s="100"/>
+      <c r="P17" s="101"/>
+    </row>
+    <row r="18" spans="2:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B18" s="106" t="s">
         <v>3</v>
       </c>
-      <c r="C18" s="78" t="s">
+      <c r="C18" s="90" t="s">
         <v>43</v>
       </c>
-      <c r="D18" s="52" t="s">
+      <c r="D18" s="73" t="s">
         <v>44</v>
       </c>
-      <c r="E18" s="52" t="s">
+      <c r="E18" s="73" t="s">
         <v>45</v>
       </c>
-      <c r="F18" s="71" t="s">
+      <c r="F18" s="82" t="s">
         <v>46</v>
       </c>
-      <c r="G18" s="84" t="s">
+      <c r="G18" s="97" t="s">
         <v>47</v>
       </c>
-      <c r="H18" s="78" t="s">
+      <c r="H18" s="90" t="s">
         <v>48</v>
       </c>
-      <c r="I18" s="79"/>
-      <c r="J18" s="52" t="s">
+      <c r="I18" s="92"/>
+      <c r="J18" s="73" t="s">
         <v>43</v>
       </c>
-      <c r="K18" s="52" t="s">
+      <c r="K18" s="73" t="s">
         <v>44</v>
       </c>
-      <c r="L18" s="71" t="s">
+      <c r="L18" s="82" t="s">
         <v>45</v>
       </c>
-      <c r="M18" s="86" t="s">
+      <c r="M18" s="102" t="s">
         <v>48</v>
       </c>
-      <c r="N18" s="52" t="s">
+      <c r="N18" s="73" t="s">
         <v>43</v>
       </c>
-      <c r="O18" s="52" t="s">
+      <c r="O18" s="73" t="s">
         <v>44</v>
       </c>
-      <c r="P18" s="71" t="s">
+      <c r="P18" s="82" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="19" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B19" s="62"/>
-      <c r="C19" s="87"/>
-      <c r="D19" s="53"/>
-      <c r="E19" s="53"/>
-      <c r="F19" s="72"/>
-      <c r="G19" s="85"/>
-      <c r="H19" s="80"/>
-      <c r="I19" s="81"/>
-      <c r="J19" s="53"/>
-      <c r="K19" s="53"/>
-      <c r="L19" s="72"/>
-      <c r="M19" s="87"/>
-      <c r="N19" s="53"/>
-      <c r="O19" s="53"/>
-      <c r="P19" s="72"/>
-    </row>
-    <row r="20" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B19" s="107"/>
+      <c r="C19" s="91"/>
+      <c r="D19" s="61"/>
+      <c r="E19" s="61"/>
+      <c r="F19" s="83"/>
+      <c r="G19" s="98"/>
+      <c r="H19" s="93"/>
+      <c r="I19" s="89"/>
+      <c r="J19" s="61"/>
+      <c r="K19" s="61"/>
+      <c r="L19" s="83"/>
+      <c r="M19" s="91"/>
+      <c r="N19" s="61"/>
+      <c r="O19" s="61"/>
+      <c r="P19" s="83"/>
+    </row>
+    <row r="20" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B20" s="42" t="s">
         <v>16</v>
       </c>
@@ -3407,10 +3428,10 @@
       <c r="G20" s="46">
         <v>1</v>
       </c>
-      <c r="H20" s="57" t="s">
+      <c r="H20" s="103" t="s">
         <v>49</v>
       </c>
-      <c r="I20" s="58"/>
+      <c r="I20" s="59"/>
       <c r="J20" s="2">
         <v>8</v>
       </c>
@@ -3433,11 +3454,31 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:16" x14ac:dyDescent="0.3">
       <c r="M21" s="3"/>
     </row>
   </sheetData>
   <mergeCells count="36">
+    <mergeCell ref="H20:I20"/>
+    <mergeCell ref="C4:C5"/>
+    <mergeCell ref="B18:B19"/>
+    <mergeCell ref="M17:P17"/>
+    <mergeCell ref="E4:E5"/>
+    <mergeCell ref="K15:L15"/>
+    <mergeCell ref="N18:N19"/>
+    <mergeCell ref="K9:L9"/>
+    <mergeCell ref="K5:L5"/>
+    <mergeCell ref="C6:C13"/>
+    <mergeCell ref="F18:F19"/>
+    <mergeCell ref="L18:L19"/>
+    <mergeCell ref="K11:L11"/>
+    <mergeCell ref="D4:D5"/>
+    <mergeCell ref="K12:L12"/>
+    <mergeCell ref="D18:D19"/>
+    <mergeCell ref="J18:J19"/>
+    <mergeCell ref="M18:M19"/>
+    <mergeCell ref="O18:O19"/>
+    <mergeCell ref="C17:F17"/>
     <mergeCell ref="P18:P19"/>
     <mergeCell ref="K7:L7"/>
     <mergeCell ref="B1:E1"/>
@@ -3454,26 +3495,6 @@
     <mergeCell ref="B3:N3"/>
     <mergeCell ref="G18:G19"/>
     <mergeCell ref="H17:L17"/>
-    <mergeCell ref="K12:L12"/>
-    <mergeCell ref="D18:D19"/>
-    <mergeCell ref="J18:J19"/>
-    <mergeCell ref="M18:M19"/>
-    <mergeCell ref="O18:O19"/>
-    <mergeCell ref="C17:F17"/>
-    <mergeCell ref="H20:I20"/>
-    <mergeCell ref="C4:C5"/>
-    <mergeCell ref="B18:B19"/>
-    <mergeCell ref="M17:P17"/>
-    <mergeCell ref="E4:E5"/>
-    <mergeCell ref="K15:L15"/>
-    <mergeCell ref="N18:N19"/>
-    <mergeCell ref="K9:L9"/>
-    <mergeCell ref="K5:L5"/>
-    <mergeCell ref="C6:C13"/>
-    <mergeCell ref="F18:F19"/>
-    <mergeCell ref="L18:L19"/>
-    <mergeCell ref="K11:L11"/>
-    <mergeCell ref="D4:D5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
